--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_software_system_application.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0434</v>
+        <v>0.0117</v>
       </c>
       <c r="E2">
-        <v>-0.206</v>
+        <v>0.435</v>
       </c>
       <c r="G2">
-        <v>-0.2046296296296296</v>
+        <v>0.2096296296296296</v>
       </c>
       <c r="H2">
-        <v>-0.2046296296296296</v>
+        <v>0.2096296296296296</v>
       </c>
       <c r="I2">
-        <v>0.2185185185185185</v>
+        <v>-0.07407407407407407</v>
       </c>
       <c r="J2">
-        <v>0.133232650125854</v>
+        <v>-0.06421744324970131</v>
       </c>
       <c r="K2">
-        <v>0.625</v>
+        <v>2.15</v>
       </c>
       <c r="L2">
-        <v>0.05787037037037036</v>
+        <v>0.1592592592592592</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,67 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="V2">
-        <v>0.002911319670561195</v>
+        <v>0.01338813857897827</v>
       </c>
       <c r="W2">
-        <v>0.01627604166666667</v>
+        <v>0.05498721227621483</v>
       </c>
       <c r="X2">
-        <v>0.07150311653346622</v>
+        <v>0.1328927693750998</v>
       </c>
       <c r="Y2">
-        <v>-0.05522707486679955</v>
+        <v>-0.07790555709888491</v>
       </c>
       <c r="Z2">
-        <v>0.2847200253084468</v>
+        <v>0.3582232128641936</v>
       </c>
       <c r="AA2">
-        <v>0.03793400351574458</v>
+        <v>-0.02300417884283203</v>
       </c>
       <c r="AB2">
-        <v>0.07149411575932231</v>
+        <v>0.1328927693750998</v>
       </c>
       <c r="AC2">
-        <v>-0.03356011224357773</v>
+        <v>-0.1558969482179318</v>
       </c>
       <c r="AD2">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.414</v>
+        <v>-2.28</v>
       </c>
       <c r="AH2">
-        <v>0.0002029850288966423</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.002703667805948069</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.002715648202563541</v>
+        <v>-0.01356981311748601</v>
       </c>
       <c r="AK2">
-        <v>-0.03752056466592368</v>
+        <v>-0.06529209621993126</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AN2">
-        <v>0.04453781512605042</v>
+        <v>-0</v>
+      </c>
+      <c r="AO2">
+        <v>-200</v>
       </c>
       <c r="AP2">
-        <v>-0.5941176470588235</v>
+        <v>2.333674513817809</v>
+      </c>
+      <c r="AQ2">
+        <v>-200</v>
       </c>
     </row>
     <row r="3">
@@ -713,28 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0434</v>
+        <v>0.0117</v>
       </c>
       <c r="E3">
-        <v>-0.206</v>
+        <v>0.435</v>
       </c>
       <c r="G3">
-        <v>-0.2046296296296296</v>
+        <v>0.2096296296296296</v>
       </c>
       <c r="H3">
-        <v>-0.2046296296296296</v>
+        <v>0.2096296296296296</v>
       </c>
       <c r="I3">
-        <v>0.2185185185185185</v>
+        <v>-0.07407407407407407</v>
       </c>
       <c r="J3">
-        <v>0.133232650125854</v>
+        <v>-0.06421744324970131</v>
       </c>
       <c r="K3">
-        <v>0.625</v>
+        <v>2.15</v>
       </c>
       <c r="L3">
-        <v>0.05787037037037036</v>
+        <v>0.1592592592592592</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,67 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>0.002911319670561195</v>
+        <v>0.01338813857897827</v>
       </c>
       <c r="W3">
-        <v>0.01627604166666667</v>
+        <v>0.05498721227621483</v>
       </c>
       <c r="X3">
-        <v>0.07150311653346622</v>
+        <v>0.1328927693750998</v>
       </c>
       <c r="Y3">
-        <v>-0.05522707486679955</v>
+        <v>-0.07790555709888491</v>
       </c>
       <c r="Z3">
-        <v>0.2847200253084468</v>
+        <v>0.3582232128641936</v>
       </c>
       <c r="AA3">
-        <v>0.03793400351574458</v>
+        <v>-0.02300417884283203</v>
       </c>
       <c r="AB3">
-        <v>0.07149411575932231</v>
+        <v>0.1328927693750998</v>
       </c>
       <c r="AC3">
-        <v>-0.03356011224357773</v>
+        <v>-0.1558969482179318</v>
       </c>
       <c r="AD3">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.414</v>
+        <v>-2.28</v>
       </c>
       <c r="AH3">
-        <v>0.0002029850288966423</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.002703667805948069</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.002715648202563541</v>
+        <v>-0.01356981311748601</v>
       </c>
       <c r="AK3">
-        <v>-0.03752056466592368</v>
+        <v>-0.06529209621993126</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AN3">
-        <v>0.04453781512605042</v>
+        <v>-0</v>
+      </c>
+      <c r="AO3">
+        <v>-200</v>
       </c>
       <c r="AP3">
-        <v>-0.5941176470588235</v>
+        <v>2.333674513817809</v>
+      </c>
+      <c r="AQ3">
+        <v>-200</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_software_system_application.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0117</v>
-      </c>
-      <c r="E2">
-        <v>0.435</v>
+        <v>-0.0495</v>
       </c>
       <c r="G2">
-        <v>0.2096296296296296</v>
+        <v>-0.2635983263598326</v>
       </c>
       <c r="H2">
-        <v>0.2096296296296296</v>
+        <v>-0.2635983263598326</v>
       </c>
       <c r="I2">
-        <v>-0.07407407407407407</v>
+        <v>-0.5209205020920502</v>
       </c>
       <c r="J2">
-        <v>-0.06421744324970131</v>
+        <v>-0.5209205020920502</v>
       </c>
       <c r="K2">
-        <v>2.15</v>
+        <v>-5.44</v>
       </c>
       <c r="L2">
-        <v>0.1592592592592592</v>
+        <v>-0.5690376569037657</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,37 +624,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.28</v>
+        <v>0.706</v>
       </c>
       <c r="V2">
-        <v>0.01338813857897827</v>
+        <v>0.003765333333333333</v>
       </c>
       <c r="W2">
-        <v>0.05498721227621483</v>
+        <v>-0.1462365591397849</v>
       </c>
       <c r="X2">
-        <v>0.1328927693750998</v>
+        <v>0.1107832977893087</v>
       </c>
       <c r="Y2">
-        <v>-0.07790555709888491</v>
+        <v>-0.2570198569290937</v>
       </c>
       <c r="Z2">
-        <v>0.3582232128641936</v>
+        <v>0.2737686139747996</v>
       </c>
       <c r="AA2">
-        <v>-0.02300417884283203</v>
+        <v>-0.1426116838487972</v>
       </c>
       <c r="AB2">
-        <v>0.1328927693750998</v>
+        <v>0.1107832977893087</v>
       </c>
       <c r="AC2">
-        <v>-0.1558969482179318</v>
+        <v>-0.2533949816381059</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2.28</v>
+        <v>-0.706</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,28 +675,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.01356981311748601</v>
+        <v>-0.003779564654110945</v>
       </c>
       <c r="AK2">
-        <v>-0.06529209621993126</v>
+        <v>-0.02277860231012454</v>
       </c>
       <c r="AL2">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="AM2">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-200</v>
+        <v>-383.0769230769232</v>
       </c>
       <c r="AP2">
-        <v>2.333674513817809</v>
+        <v>0.142914979757085</v>
       </c>
       <c r="AQ2">
-        <v>-200</v>
+        <v>-383.0769230769232</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0117</v>
-      </c>
-      <c r="E3">
-        <v>0.435</v>
+        <v>-0.0495</v>
       </c>
       <c r="G3">
-        <v>0.2096296296296296</v>
+        <v>-0.2635983263598326</v>
       </c>
       <c r="H3">
-        <v>0.2096296296296296</v>
+        <v>-0.2635983263598326</v>
       </c>
       <c r="I3">
-        <v>-0.07407407407407407</v>
+        <v>-0.5209205020920502</v>
       </c>
       <c r="J3">
-        <v>-0.06421744324970131</v>
+        <v>-0.5209205020920502</v>
       </c>
       <c r="K3">
-        <v>2.15</v>
+        <v>-5.44</v>
       </c>
       <c r="L3">
-        <v>0.1592592592592592</v>
+        <v>-0.5690376569037657</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,37 +752,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>0.706</v>
       </c>
       <c r="V3">
-        <v>0.01338813857897827</v>
+        <v>0.003765333333333333</v>
       </c>
       <c r="W3">
-        <v>0.05498721227621483</v>
+        <v>-0.1462365591397849</v>
       </c>
       <c r="X3">
-        <v>0.1328927693750998</v>
+        <v>0.1107832977893087</v>
       </c>
       <c r="Y3">
-        <v>-0.07790555709888491</v>
+        <v>-0.2570198569290937</v>
       </c>
       <c r="Z3">
-        <v>0.3582232128641936</v>
+        <v>0.2737686139747996</v>
       </c>
       <c r="AA3">
-        <v>-0.02300417884283203</v>
+        <v>-0.1426116838487972</v>
       </c>
       <c r="AB3">
-        <v>0.1328927693750998</v>
+        <v>0.1107832977893087</v>
       </c>
       <c r="AC3">
-        <v>-0.1558969482179318</v>
+        <v>-0.2533949816381059</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.28</v>
+        <v>-0.706</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,28 +803,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01356981311748601</v>
+        <v>-0.003779564654110945</v>
       </c>
       <c r="AK3">
-        <v>-0.06529209621993126</v>
+        <v>-0.02277860231012454</v>
       </c>
       <c r="AL3">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="AM3">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-200</v>
+        <v>-383.0769230769232</v>
       </c>
       <c r="AP3">
-        <v>2.333674513817809</v>
+        <v>0.142914979757085</v>
       </c>
       <c r="AQ3">
-        <v>-200</v>
+        <v>-383.0769230769232</v>
       </c>
     </row>
   </sheetData>
